--- a/docs/rag_file_index_rev1.xlsx
+++ b/docs/rag_file_index_rev1.xlsx
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>1.6 KB</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>14.6 KB</t>
+          <t>17.3 KB</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>1.4 KB</t>
+          <t>1.6 KB</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>45.1 KB</t>
+          <t>50.7 KB</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
@@ -2910,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2933,7 +2933,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>전체 300 개 · 코드에서 자동 추출 · G · H 열 기입</t>
+          <t>전체 338 개 · 코드에서 자동 추출 · G · H 열 기입</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr"/>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>os.path.dirname(os.path.abspath(__file__))</t>
+        </is>
+      </c>
       <c r="F28" s="21" t="n">
         <v>13</v>
       </c>
@@ -3754,7 +3758,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr"/>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>os.path.join(LAB_DIR, 'out')</t>
+        </is>
+      </c>
       <c r="F29" s="21" t="n">
         <v>14</v>
       </c>
@@ -3782,7 +3790,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>os.path.join(LAB_DIR, 'golden')</t>
+        </is>
+      </c>
       <c r="F30" s="21" t="n">
         <v>15</v>
       </c>
@@ -3874,7 +3886,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr"/>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>LAB_MODE == 'sample'</t>
+        </is>
+      </c>
       <c r="F33" s="21" t="n">
         <v>38</v>
       </c>
@@ -3902,7 +3918,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr"/>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>env('ORA_USER')</t>
+        </is>
+      </c>
       <c r="F34" s="21" t="n">
         <v>41</v>
       </c>
@@ -3930,7 +3950,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>env('ORA_PASSWORD')</t>
+        </is>
+      </c>
       <c r="F35" s="21" t="n">
         <v>42</v>
       </c>
@@ -4022,7 +4046,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr"/>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>env('MILVUS_URI', 'http://localhost:19530')</t>
+        </is>
+      </c>
       <c r="F38" s="21" t="n">
         <v>47</v>
       </c>
@@ -4050,7 +4078,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr"/>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>env('MILVUS_TOKEN', '')</t>
+        </is>
+      </c>
       <c r="F39" s="21" t="n">
         <v>48</v>
       </c>
@@ -4078,7 +4110,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr"/>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>env('MILVUS_COLLECTION', 'rag_chunks')</t>
+        </is>
+      </c>
       <c r="F40" s="21" t="n">
         <v>49</v>
       </c>
@@ -4202,7 +4238,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>env('EMBED_MODEL', 'bge-m3')</t>
+        </is>
+      </c>
       <c r="F44" s="21" t="n">
         <v>55</v>
       </c>
@@ -4294,7 +4334,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr"/>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>env('RERANK_PATH', '')</t>
+        </is>
+      </c>
       <c r="F47" s="21" t="n">
         <v>59</v>
       </c>
@@ -4322,7 +4366,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr"/>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>env('RERANK_URL', '')</t>
+        </is>
+      </c>
       <c r="F48" s="21" t="n">
         <v>60</v>
       </c>
@@ -4382,7 +4430,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr"/>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>env('LLM_MODEL', '')</t>
+        </is>
+      </c>
       <c r="F50" s="21" t="n">
         <v>63</v>
       </c>
@@ -4410,7 +4462,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr"/>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>env('LLM_API_KEY', 'none')</t>
+        </is>
+      </c>
       <c r="F51" s="21" t="n">
         <v>64</v>
       </c>
@@ -4438,7 +4494,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr"/>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>env('SEARCH_API_URL', '')</t>
+        </is>
+      </c>
       <c r="F52" s="21" t="n">
         <v>67</v>
       </c>
@@ -4466,7 +4526,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>env('SEARCH_API_TOKEN', '')</t>
+        </is>
+      </c>
       <c r="F53" s="21" t="n">
         <v>68</v>
       </c>
@@ -4494,7 +4558,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E54" s="20" t="inlineStr"/>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>env('SAMPLE_MODELS', 'false').lower() == 'true'</t>
+        </is>
+      </c>
       <c r="F54" s="21" t="n">
         <v>73</v>
       </c>
@@ -4522,7 +4590,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>env('SAMPLE_SET', '16')</t>
+        </is>
+      </c>
       <c r="F55" s="21" t="n">
         <v>75</v>
       </c>
@@ -4550,7 +4622,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr"/>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>bool(LLM_URL) and (not IS_SAMPLE or SAMPLE_MODELS)</t>
+        </is>
+      </c>
       <c r="F56" s="21" t="n">
         <v>80</v>
       </c>
@@ -4578,7 +4654,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr"/>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>int(env('HTTP_TIMEOUT', '60'))</t>
+        </is>
+      </c>
       <c r="F57" s="21" t="n">
         <v>82</v>
       </c>
@@ -4606,7 +4686,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr"/>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>env('VERIFY_SSL', 'false').lower() == 'true'</t>
+        </is>
+      </c>
       <c r="F58" s="21" t="n">
         <v>83</v>
       </c>
@@ -4634,7 +4718,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr"/>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>dict(table='RAG_RAW_DOC', doc_id='DOC_ID', doc_type='DOC_TYPE', title=</t>
+        </is>
+      </c>
       <c r="F59" s="21" t="n">
         <v>94</v>
       </c>
@@ -4662,7 +4750,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E60" s="20" t="inlineStr"/>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>dict(table='RAG_CHUNK', chunk_id='CHUNK_ID', doc_id='DOC_ID', seq='CHU</t>
+        </is>
+      </c>
       <c r="F60" s="21" t="n">
         <v>108</v>
       </c>
@@ -4754,7 +4846,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr"/>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>dict(request=lambda q, k: {'query': q, 'top_k': k}, results_key='resul</t>
+        </is>
+      </c>
       <c r="F63" s="21" t="n">
         <v>135</v>
       </c>
@@ -8210,7 +8306,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E173" s="20" t="inlineStr"/>
+      <c r="E173" s="20" t="inlineStr">
+        <is>
+          <t>[f'2026-{m:02d}' for m in range(4, 10)]</t>
+        </is>
+      </c>
       <c r="F173" s="21" t="n">
         <v>33</v>
       </c>
@@ -8710,7 +8810,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E190" s="20" t="inlineStr"/>
+      <c r="E190" s="20" t="inlineStr">
+        <is>
+          <t>{c: lab_sources.security(c) for c in PREFIX}</t>
+        </is>
+      </c>
       <c r="F190" s="21" t="n">
         <v>223</v>
       </c>
@@ -10837,7 +10941,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E261" s="20" t="inlineStr"/>
+      <c r="E261" s="20" t="inlineStr">
+        <is>
+          <t>os.path.join(C.LAB_DIR, 'catalog')</t>
+        </is>
+      </c>
       <c r="F261" s="21" t="n">
         <v>17</v>
       </c>
@@ -10865,7 +10973,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E262" s="20" t="inlineStr"/>
+      <c r="E262" s="20" t="inlineStr">
+        <is>
+          <t>os.path.join(CAT_DIR, 'metric_catalog.xlsx')</t>
+        </is>
+      </c>
       <c r="F262" s="21" t="n">
         <v>18</v>
       </c>
@@ -10893,7 +11005,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E263" s="20" t="inlineStr"/>
+      <c r="E263" s="20" t="inlineStr">
+        <is>
+          <t>os.path.join(CAT_DIR, 'metric_catalog_example.xlsx')</t>
+        </is>
+      </c>
       <c r="F263" s="21" t="n">
         <v>19</v>
       </c>
@@ -10921,7 +11037,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E264" s="20" t="inlineStr"/>
+      <c r="E264" s="20" t="inlineStr">
+        <is>
+          <t>int(C.env('SQL_MAX_ROWS', '200'))</t>
+        </is>
+      </c>
       <c r="F264" s="21" t="n">
         <v>20</v>
       </c>
@@ -10949,7 +11069,11 @@
           <t>설정값</t>
         </is>
       </c>
-      <c r="E265" s="20" t="inlineStr"/>
+      <c r="E265" s="20" t="inlineStr">
+        <is>
+          <t>int(C.env('SQL_TIMEOUT', '20'))</t>
+        </is>
+      </c>
       <c r="F265" s="21" t="n">
         <v>21</v>
       </c>
@@ -12176,43 +12300,1247 @@
       <c r="G304" s="11" t="inlineStr"/>
       <c r="H304" s="12" t="inlineStr"/>
     </row>
+    <row r="305">
+      <c r="A305" s="20" t="inlineStr">
+        <is>
+          <t>nb01_inventory.py</t>
+        </is>
+      </c>
+      <c r="B305" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C305" s="20" t="inlineStr">
+        <is>
+          <t>N_PER_TYPE</t>
+        </is>
+      </c>
+      <c r="D305" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E305" s="20" t="inlineStr">
+        <is>
+          <t>값 = 50</t>
+        </is>
+      </c>
+      <c r="F305" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G305" s="11" t="inlineStr"/>
+      <c r="H305" s="12" t="inlineStr"/>
+    </row>
     <row r="306">
-      <c r="A306" s="16" t="inlineStr">
+      <c r="A306" s="20" t="inlineStr">
+        <is>
+          <t>nb01_inventory.py</t>
+        </is>
+      </c>
+      <c r="B306" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C306" s="20" t="inlineStr">
+        <is>
+          <t>META_COLS</t>
+        </is>
+      </c>
+      <c r="D306" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E306" s="20" t="inlineStr">
+        <is>
+          <t>[c for c in ('title', 'published_at', 'org_name', 'author', 'security_</t>
+        </is>
+      </c>
+      <c r="F306" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G306" s="11" t="inlineStr"/>
+      <c r="H306" s="12" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>nb01_inventory.py</t>
+        </is>
+      </c>
+      <c r="B307" s="10" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>_store(g)</t>
+        </is>
+      </c>
+      <c r="D307" s="10" t="inlineStr">
+        <is>
+          <t>함수</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr"/>
+      <c r="F307" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G307" s="11" t="inlineStr"/>
+      <c r="H307" s="12" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="20" t="inlineStr">
+        <is>
+          <t>nb02_parse_chunk.py</t>
+        </is>
+      </c>
+      <c r="B308" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C308" s="20" t="inlineStr">
+        <is>
+          <t>N_PER_TYPE</t>
+        </is>
+      </c>
+      <c r="D308" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E308" s="20" t="inlineStr">
+        <is>
+          <t>값 = 30</t>
+        </is>
+      </c>
+      <c r="F308" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G308" s="11" t="inlineStr"/>
+      <c r="H308" s="12" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="20" t="inlineStr">
+        <is>
+          <t>nb02_parse_chunk.py</t>
+        </is>
+      </c>
+      <c r="B309" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr">
+        <is>
+          <t>DOC_ID</t>
+        </is>
+      </c>
+      <c r="D309" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E309" s="20" t="inlineStr">
+        <is>
+          <t>raw_s.loc[raw_s.doc_type == 'EMAIL', 'doc_id'].iloc[0] if (raw_s.doc_t</t>
+        </is>
+      </c>
+      <c r="F309" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="G309" s="11" t="inlineStr"/>
+      <c r="H309" s="12" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="20" t="inlineStr">
+        <is>
+          <t>nb03_bm25_tokenizer.py</t>
+        </is>
+      </c>
+      <c r="B310" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C310" s="20" t="inlineStr">
+        <is>
+          <t>SENTENCES</t>
+        </is>
+      </c>
+      <c r="D310" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E310" s="20" t="inlineStr">
+        <is>
+          <t>목록 4 개</t>
+        </is>
+      </c>
+      <c r="F310" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G310" s="11" t="inlineStr"/>
+      <c r="H310" s="12" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="20" t="inlineStr">
+        <is>
+          <t>nb03_bm25_tokenizer.py</t>
+        </is>
+      </c>
+      <c r="B311" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr">
+        <is>
+          <t>TOKENIZERS</t>
+        </is>
+      </c>
+      <c r="D311" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E311" s="20" t="inlineStr">
+        <is>
+          <t>목록 3 개</t>
+        </is>
+      </c>
+      <c r="F311" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G311" s="11" t="inlineStr"/>
+      <c r="H311" s="12" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="20" t="inlineStr">
+        <is>
+          <t>nb03_bm25_tokenizer.py</t>
+        </is>
+      </c>
+      <c r="B312" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C312" s="20" t="inlineStr">
+        <is>
+          <t>CORPUS_N</t>
+        </is>
+      </c>
+      <c r="D312" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E312" s="20" t="inlineStr">
+        <is>
+          <t>live: 불러올 청크 수 (메모리에 맞게)</t>
+        </is>
+      </c>
+      <c r="F312" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="G312" s="11" t="inlineStr"/>
+      <c r="H312" s="12" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="20" t="inlineStr">
+        <is>
+          <t>nb03_bm25_tokenizer.py</t>
+        </is>
+      </c>
+      <c r="B313" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr">
+        <is>
+          <t>QUERY</t>
+        </is>
+      </c>
+      <c r="D313" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E313" s="20" t="inlineStr">
+        <is>
+          <t>값 = 하이닉스의 HBM 점유율 추정치는?</t>
+        </is>
+      </c>
+      <c r="F313" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="G313" s="11" t="inlineStr"/>
+      <c r="H313" s="12" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="20" t="inlineStr">
+        <is>
+          <t>nb04_milvus.py</t>
+        </is>
+      </c>
+      <c r="B314" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C314" s="20" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D314" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E314" s="20" t="inlineStr">
+        <is>
+          <t>not C.IS_SAMPLE</t>
+        </is>
+      </c>
+      <c r="F314" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G314" s="11" t="inlineStr"/>
+      <c r="H314" s="12" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="20" t="inlineStr">
+        <is>
+          <t>nb04_milvus.py</t>
+        </is>
+      </c>
+      <c r="B315" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>NEED</t>
+        </is>
+      </c>
+      <c r="D315" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E315" s="20" t="inlineStr">
+        <is>
+          <t>딕셔너리 8 항목</t>
+        </is>
+      </c>
+      <c r="F315" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G315" s="11" t="inlineStr"/>
+      <c r="H315" s="12" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="20" t="inlineStr">
+        <is>
+          <t>nb04_milvus.py</t>
+        </is>
+      </c>
+      <c r="B316" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C316" s="20" t="inlineStr">
+        <is>
+          <t>QUERY</t>
+        </is>
+      </c>
+      <c r="D316" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E316" s="20" t="inlineStr">
+        <is>
+          <t>값 = 3분기 DRAM 계약가격 전망</t>
+        </is>
+      </c>
+      <c r="F316" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G316" s="11" t="inlineStr"/>
+      <c r="H316" s="12" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="20" t="inlineStr">
+        <is>
+          <t>nb04_milvus.py</t>
+        </is>
+      </c>
+      <c r="B317" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C317" s="20" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="D317" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E317" s="20" t="inlineStr">
+        <is>
+          <t>사내 필드 · 값에 맞게</t>
+        </is>
+      </c>
+      <c r="F317" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="G317" s="11" t="inlineStr"/>
+      <c r="H317" s="12" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="20" t="inlineStr">
+        <is>
+          <t>nb05_smoke_test.py</t>
+        </is>
+      </c>
+      <c r="B318" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C318" s="20" t="inlineStr">
+        <is>
+          <t>HOW</t>
+        </is>
+      </c>
+      <c r="D318" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E318" s="20" t="inlineStr">
+        <is>
+          <t>'api' if C.SEARCH_API_URL and (not C.IS_SAMPLE) else 'lab'</t>
+        </is>
+      </c>
+      <c r="F318" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G318" s="11" t="inlineStr"/>
+      <c r="H318" s="12" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="20" t="inlineStr">
+        <is>
+          <t>nb05_smoke_test.py</t>
+        </is>
+      </c>
+      <c r="B319" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C319" s="20" t="inlineStr">
+        <is>
+          <t>JUDGED</t>
+        </is>
+      </c>
+      <c r="D319" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E319" s="20" t="inlineStr">
+        <is>
+          <t>← 판정을 채운 파일 경로</t>
+        </is>
+      </c>
+      <c r="F319" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G319" s="11" t="inlineStr"/>
+      <c r="H319" s="12" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B320" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="inlineStr">
+        <is>
+          <t>PARTS</t>
+        </is>
+      </c>
+      <c r="D320" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E320" s="20" t="inlineStr">
+        <is>
+          <t>live 에서 sparse 필드가 없으면 ('bm25', 'dense')</t>
+        </is>
+      </c>
+      <c r="F320" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G320" s="11" t="inlineStr"/>
+      <c r="H320" s="12" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B321" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr">
+        <is>
+          <t>BM25_TOK</t>
+        </is>
+      </c>
+      <c r="D321" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E321" s="20" t="inlineStr">
+        <is>
+          <t>space | josa | kiwi</t>
+        </is>
+      </c>
+      <c r="F321" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="G321" s="11" t="inlineStr"/>
+      <c r="H321" s="12" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B322" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="inlineStr">
+        <is>
+          <t>CORPUS_N</t>
+        </is>
+      </c>
+      <c r="D322" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E322" s="20" t="inlineStr">
+        <is>
+          <t>값 = 50000</t>
+        </is>
+      </c>
+      <c r="F322" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G322" s="11" t="inlineStr"/>
+      <c r="H322" s="12" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B323" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>MODES</t>
+        </is>
+      </c>
+      <c r="D323" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E323" s="20" t="inlineStr">
+        <is>
+          <t>목록 6 개</t>
+        </is>
+      </c>
+      <c r="F323" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G323" s="11" t="inlineStr"/>
+      <c r="H323" s="12" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B324" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C324" s="20" t="inlineStr">
+        <is>
+          <t>MODES</t>
+        </is>
+      </c>
+      <c r="D324" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E324" s="20" t="inlineStr">
+        <is>
+          <t>[m for m in MODES if m not in ('bm25', 'dense', 'sparse') or m in PART</t>
+        </is>
+      </c>
+      <c r="F324" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G324" s="11" t="inlineStr"/>
+      <c r="H324" s="12" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B325" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C325" s="20" t="inlineStr">
+        <is>
+          <t>MODE</t>
+        </is>
+      </c>
+      <c r="D325" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E325" s="20" t="inlineStr">
+        <is>
+          <t>값 = hybrid+rerank+mmr</t>
+        </is>
+      </c>
+      <c r="F325" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="G325" s="11" t="inlineStr"/>
+      <c r="H325" s="12" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="20" t="inlineStr">
+        <is>
+          <t>nb06_retrieval_eval.py</t>
+        </is>
+      </c>
+      <c r="B326" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C326" s="20" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="D326" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E326" s="20" t="inlineStr">
+        <is>
+          <t>golden.qid.iloc[0]</t>
+        </is>
+      </c>
+      <c r="F326" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="G326" s="11" t="inlineStr"/>
+      <c r="H326" s="12" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="20" t="inlineStr">
+        <is>
+          <t>nb07_sql_router.py</t>
+        </is>
+      </c>
+      <c r="B327" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C327" s="20" t="inlineStr">
+        <is>
+          <t>QUESTIONS</t>
+        </is>
+      </c>
+      <c r="D327" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E327" s="20" t="inlineStr">
+        <is>
+          <t>목록 6 개</t>
+        </is>
+      </c>
+      <c r="F327" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G327" s="11" t="inlineStr"/>
+      <c r="H327" s="12" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="20" t="inlineStr">
+        <is>
+          <t>nb07_sql_router.py</t>
+        </is>
+      </c>
+      <c r="B328" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="inlineStr">
+        <is>
+          <t>QUESTION</t>
+        </is>
+      </c>
+      <c r="D328" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E328" s="20" t="inlineStr">
+        <is>
+          <t>값 = 2026년 3분기 eSSD 출하량은?</t>
+        </is>
+      </c>
+      <c r="F328" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G328" s="11" t="inlineStr"/>
+      <c r="H328" s="12" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="20" t="inlineStr">
+        <is>
+          <t>nb07_sql_router.py</t>
+        </is>
+      </c>
+      <c r="B329" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C329" s="20" t="inlineStr">
+        <is>
+          <t>BAD</t>
+        </is>
+      </c>
+      <c r="D329" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E329" s="20" t="inlineStr">
+        <is>
+          <t>딕셔너리 4 항목</t>
+        </is>
+      </c>
+      <c r="F329" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G329" s="11" t="inlineStr"/>
+      <c r="H329" s="12" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="20" t="inlineStr">
+        <is>
+          <t>nb07_sql_router.py</t>
+        </is>
+      </c>
+      <c r="B330" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C330" s="20" t="inlineStr">
+        <is>
+          <t>HYBRID_Q</t>
+        </is>
+      </c>
+      <c r="D330" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E330" s="20" t="inlineStr">
+        <is>
+          <t>값 = 3분기 eSSD 출하량과 그렇게 본 이유는?</t>
+        </is>
+      </c>
+      <c r="F330" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G330" s="11" t="inlineStr"/>
+      <c r="H330" s="12" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="20" t="inlineStr">
+        <is>
+          <t>nb08_auto_eval.py</t>
+        </is>
+      </c>
+      <c r="B331" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C331" s="20" t="inlineStr">
+        <is>
+          <t>N_KNOWN</t>
+        </is>
+      </c>
+      <c r="D331" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E331" s="20" t="inlineStr">
+        <is>
+          <t>값 = 200</t>
+        </is>
+      </c>
+      <c r="F331" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G331" s="11" t="inlineStr"/>
+      <c r="H331" s="12" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="20" t="inlineStr">
+        <is>
+          <t>nb08_auto_eval.py</t>
+        </is>
+      </c>
+      <c r="B332" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C332" s="20" t="inlineStr">
+        <is>
+          <t>N_SYN</t>
+        </is>
+      </c>
+      <c r="D332" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E332" s="20" t="inlineStr">
+        <is>
+          <t>값 = 50</t>
+        </is>
+      </c>
+      <c r="F332" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="G332" s="11" t="inlineStr"/>
+      <c r="H332" s="12" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t>nb08_auto_eval.py</t>
+        </is>
+      </c>
+      <c r="B333" s="10" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>run(eval_df, name, k)</t>
+        </is>
+      </c>
+      <c r="D333" s="10" t="inlineStr">
+        <is>
+          <t>함수</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr"/>
+      <c r="F333" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G333" s="11" t="inlineStr"/>
+      <c r="H333" s="12" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>nb08_auto_eval.py</t>
+        </is>
+      </c>
+      <c r="B334" s="10" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>_judge(row)</t>
+        </is>
+      </c>
+      <c r="D334" s="10" t="inlineStr">
+        <is>
+          <t>함수</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr"/>
+      <c r="F334" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="G334" s="11" t="inlineStr"/>
+      <c r="H334" s="12" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="20" t="inlineStr">
+        <is>
+          <t>nb09_golden_build.py</t>
+        </is>
+      </c>
+      <c r="B335" s="21" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C335" s="20" t="inlineStr">
+        <is>
+          <t>REVIEWED</t>
+        </is>
+      </c>
+      <c r="D335" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E335" s="20" t="inlineStr">
+        <is>
+          <t>← 검수 완료 파일 경로로 교체</t>
+        </is>
+      </c>
+      <c r="F335" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G335" s="11" t="inlineStr"/>
+      <c r="H335" s="12" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="20" t="inlineStr">
+        <is>
+          <t>nb10_answer_eval.py</t>
+        </is>
+      </c>
+      <c r="B336" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C336" s="20" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
+      <c r="D336" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E336" s="20" t="inlineStr">
+        <is>
+          <t>_linked if os.path.exists(_linked) else os.path.join(C.GOLDEN_DIR, 'an</t>
+        </is>
+      </c>
+      <c r="F336" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G336" s="11" t="inlineStr"/>
+      <c r="H336" s="12" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="20" t="inlineStr">
+        <is>
+          <t>nb10_answer_eval.py</t>
+        </is>
+      </c>
+      <c r="B337" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C337" s="20" t="inlineStr">
+        <is>
+          <t>THRESH</t>
+        </is>
+      </c>
+      <c r="D337" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E337" s="20" t="inlineStr">
+        <is>
+          <t>딕셔너리 6 항목</t>
+        </is>
+      </c>
+      <c r="F337" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="G337" s="11" t="inlineStr"/>
+      <c r="H337" s="12" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="20" t="inlineStr">
+        <is>
+          <t>nb11_evidence_link.py</t>
+        </is>
+      </c>
+      <c r="B338" s="21" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C338" s="20" t="inlineStr">
+        <is>
+          <t>LINKED</t>
+        </is>
+      </c>
+      <c r="D338" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E338" s="20" t="inlineStr">
+        <is>
+          <t>← 판정 완료 파일 경로</t>
+        </is>
+      </c>
+      <c r="F338" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G338" s="11" t="inlineStr"/>
+      <c r="H338" s="12" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="20" t="inlineStr">
+        <is>
+          <t>nb12_golden_llm.py</t>
+        </is>
+      </c>
+      <c r="B339" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C339" s="20" t="inlineStr">
+        <is>
+          <t>USE_LLM</t>
+        </is>
+      </c>
+      <c r="D339" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E339" s="20" t="inlineStr">
+        <is>
+          <t>C.USE_LLM</t>
+        </is>
+      </c>
+      <c r="F339" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G339" s="11" t="inlineStr"/>
+      <c r="H339" s="12" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="20" t="inlineStr">
+        <is>
+          <t>nb12_golden_llm.py</t>
+        </is>
+      </c>
+      <c r="B340" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C340" s="20" t="inlineStr">
+        <is>
+          <t>REVIEWED</t>
+        </is>
+      </c>
+      <c r="D340" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E340" s="20" t="inlineStr">
+        <is>
+          <t>예: r'C:\work\rag_lab\out\nb12_golden_review_260924_101500.xlsx'</t>
+        </is>
+      </c>
+      <c r="F340" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G340" s="11" t="inlineStr"/>
+      <c r="H340" s="12" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="20" t="inlineStr">
+        <is>
+          <t>nb13_langgraph_rag.py</t>
+        </is>
+      </c>
+      <c r="B341" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C341" s="20" t="inlineStr">
+        <is>
+          <t>GSRC</t>
+        </is>
+      </c>
+      <c r="D341" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E341" s="20" t="inlineStr">
+        <is>
+          <t>_g if os.path.exists(_g) else os.path.join(C.GOLDEN_DIR, 'answer_golde</t>
+        </is>
+      </c>
+      <c r="F341" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G341" s="11" t="inlineStr"/>
+      <c r="H341" s="12" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="20" t="inlineStr">
+        <is>
+          <t>nb13_langgraph_rag.py</t>
+        </is>
+      </c>
+      <c r="B342" s="21" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="C342" s="20" t="inlineStr">
+        <is>
+          <t>PRESETS</t>
+        </is>
+      </c>
+      <c r="D342" s="21" t="inlineStr">
+        <is>
+          <t>설정값</t>
+        </is>
+      </c>
+      <c r="E342" s="20" t="inlineStr">
+        <is>
+          <t>목록 6 개</t>
+        </is>
+      </c>
+      <c r="F342" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="G342" s="11" t="inlineStr"/>
+      <c r="H342" s="12" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="16" t="inlineStr">
         <is>
           <t>집계</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" s="17" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="17" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="B307" s="18">
-        <f>COUNTIF(C5:C304,"&lt;&gt;")</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="17" t="inlineStr">
+      <c r="B345" s="18">
+        <f>COUNTIF(C5:C342,"&lt;&gt;")</f>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="17" t="inlineStr">
         <is>
           <t>확인 완료</t>
         </is>
       </c>
-      <c r="B308" s="18">
-        <f>COUNTIF(G5:G304,"확인")</f>
+      <c r="B346" s="18">
+        <f>COUNTIF(G5:G342,"확인")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="17" t="inlineStr">
+    <row r="347">
+      <c r="A347" s="17" t="inlineStr">
         <is>
           <t>진행률</t>
         </is>
       </c>
-      <c r="B309" s="19">
-        <f>IFERROR(COUNTIF(G5:G304,"확인")/COUNTIF(C5:C304,"&lt;&gt;"),"")</f>
+      <c r="B347" s="19">
+        <f>IFERROR(COUNTIF(G5:G342,"확인")/COUNTIF(C5:C342,"&lt;&gt;"),"")</f>
         <v>0.0</v>
       </c>
     </row>
@@ -12221,7 +13549,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G304">
+  <conditionalFormatting sqref="G5:G342">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"확인"</formula>
     </cfRule>
@@ -12230,7 +13558,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G342" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확인,보류,질문 있음"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12245,16 +13573,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12267,7 +13597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>전체 112 셀 · 위에서 아래로 실행 · F · G 열 기입</t>
+          <t>전체 112 셀 · 위에서 아래로 실행 · H · I 열 기입</t>
         </is>
       </c>
     </row>
@@ -12294,15 +13624,25 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>이 셀이 호출하는 함수</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>만들어지는 변수 (Variable Explorer)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>참조 문서</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -12329,11 +13669,21 @@
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
+          <t>pd.Series · C.summary</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [단계별_실행도구] S00 · [P1_적재공통] 전체</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr"/>
-      <c r="G5" s="24" t="inlineStr"/>
+      <c r="H5" s="25" t="inlineStr"/>
+      <c r="I5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12354,9 +13704,19 @@
       <c r="D6" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="12" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_raw · lab_io.load_chunks</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>raw · chunks</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -12377,9 +13737,19 @@
       <c r="D7" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.unmapped · lab_sources.table</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>chk</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -12400,9 +13770,19 @@
       <c r="D8" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.type_distribution</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>dist</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -12423,9 +13803,19 @@
       <c r="D9" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.doc_integrity</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>doc_chk</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -12446,9 +13836,19 @@
       <c r="D10" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.meta_completeness</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>meta_chk</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -12469,9 +13869,19 @@
       <c r="D11" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.chunk_integrity</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>chunk_chk</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -12492,9 +13902,19 @@
       <c r="D12" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.chunk_size_profile</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -12515,9 +13935,19 @@
       <c r="D13" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.index_integrity</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>idx_chk</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -12538,9 +13968,19 @@
       <c r="D14" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>lab_pipeline.pipeline_report · lab_pipeline.failed_only</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>rep · fail</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -12561,9 +14001,15 @@
       <c r="D15" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -12586,11 +14032,21 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
+          <t>pd.Series · C.summary</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>cfg · LAB</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_적재공통] S01 수집 · S05 메타데이터</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr"/>
-      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -12611,9 +14067,19 @@
       <c r="D17" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.count_by_type · lab_io.count_chunks_by_type · docs_by_type.merge · map</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>docs_by_type · chunks_by_type · inv</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -12634,9 +14100,19 @@
       <c r="D18" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.sample_per_type · raw_s.doc_type.nunique</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>N_PER_TYPE · raw_s</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -12657,9 +14133,19 @@
       <c r="D19" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>meta_fill.insert · meta_fill.index.map · apply · raw_s.groupby · mean · g.notna</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>META_COLS · meta_fill</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -12680,9 +14166,19 @@
       <c r="D20" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>apply · store_check.insert · pd.Series · store_check.index.map · raw_s.groupby · median</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>store_check · b</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -12703,9 +14199,19 @@
       <c r="D21" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>map · lab_text.near_duplicates · lab_text.clean · raw_s.set_index · dup_near.id_a.map · dup_near.id_b.map</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>dup_exact · dup_near · t</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -12726,9 +14232,15 @@
       <c r="D22" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="12" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>inv.iterrows · lab_io.save · meta_fill.reset_index · store_check.reset_index · pd.notna</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
@@ -12751,11 +14263,21 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
+          <t>lab_text.tokenizer</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_적재공통] S02 파싱 · S03 청킹 · S04 임베딩</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr"/>
-      <c r="G23" s="24" t="inlineStr"/>
+      <c r="H23" s="25" t="inlineStr"/>
+      <c r="I23" s="24" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -12776,9 +14298,19 @@
       <c r="D24" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="12" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.sample_per_type · lab_io.load_chunks · ch.merge · tolist</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>N_PER_TYPE · raw_s · ch</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -12799,9 +14331,19 @@
       <c r="D25" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>str.len · map · agg · chunk_stats.insert · chunk_stats.index.map · ch.groupby</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>chunk_stats</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -12822,9 +14364,19 @@
       <c r="D26" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>map · chunk_quality.insert · lab_text.noise_left · lab_text.has_header · chunk_quality.index.map · mean</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>chunk_quality</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -12845,9 +14397,19 @@
       <c r="D27" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>agg · clean_cmp.insert · lab_text.clean · lab_text.noise_left · clean_cmp.index.map · raw_s.groupby</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>clean_cmp</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -12868,9 +14430,19 @@
       <c r="D28" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>doc_view.itertuples · any · raw_s.set_index</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>DOC_ID · doc_view</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -12891,9 +14463,19 @@
       <c r="D29" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>lab_text.build_header · raw_s.to_dict</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>header_preview</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -12914,9 +14496,15 @@
       <c r="D30" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · chunk_stats.reset_index · chunk_quality.reset_index · clean_cmp.reset_index</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -12937,9 +14525,19 @@
       <c r="D31" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>raw_s.groupby · pd.DataFrame · lab_sources.chunk_opts · str.len · rows.append · lab_text.chunk_text</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>rows · rechunk · now · re_ch</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -12960,13 +14558,19 @@
       <c r="D32" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>S · LAB</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_검색] S09 BM25</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr"/>
-      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="14" t="inlineStr"/>
+      <c r="I32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -12987,9 +14591,19 @@
       <c r="D33" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · S.get_tokenizer</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>SENTENCES · TOKENIZERS · tok_cmp</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -13010,9 +14624,19 @@
       <c r="D34" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="12" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>golden.fillna · lab_io.read_table · golden · dropna · lab_io.sample_mod · lab_io.load_chunks</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>CORPUS_N · corpus · golden</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -13033,9 +14657,19 @@
       <c r="D35" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>drop_duplicates · pd.concat · lab_io.load_chunks</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>corpus</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -13056,9 +14690,19 @@
       <c r="D36" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr"/>
-      <c r="G36" s="12" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>bm25_models.items · pd.DataFrame · fit · itertuples · tolist · S.Retriever._rank</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>bm25_models · rows · bm25_detail · bm25_cmp · res · rel</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -13079,9 +14723,19 @@
       <c r="D37" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr"/>
-      <c r="G37" s="12" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>pd.concat · bm25_models.items · bm.search</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>QUERY · drill</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -13102,9 +14756,15 @@
       <c r="D38" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr"/>
-      <c r="G38" s="12" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · rename · bm25_cmp.reset_index · tok_cmp.reset_index</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
@@ -13125,13 +14785,19 @@
       <c r="D39" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr"/>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>LIVE · LAB</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_적재공통] S06 벡터DB · [P1_검색] S10 시맨틱 검색</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr"/>
-      <c r="G39" s="15" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="15" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -13152,9 +14818,19 @@
       <c r="D40" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="11" t="inlineStr"/>
-      <c r="G40" s="12" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.MilvusSearcher · mv.describe · pd.DataFrame · getattr · connections.connect · utility.get_server_version</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>mv · server_version · mv_fields · mv_indexes · mv_count</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
+      <c r="I40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -13175,9 +14851,19 @@
       <c r="D41" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr"/>
-      <c r="G41" s="12" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · str.upper · NEED.items · any · k.split</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>NEED · field_check</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -13198,9 +14884,19 @@
       <c r="D42" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="11" t="inlineStr"/>
-      <c r="G42" s="12" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · lab_io.load_chunks · lab_io.read_sql</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>sync_check · oracle_chunks</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -13221,9 +14917,19 @@
       <c r="D43" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
-      <c r="G43" s="12" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.Embedder · mv.dense · lab_search.Retriever · ret.dense · pd.DataFrame · lab_io.load_chunks</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>QUERY · FILTER · emb · v · mv_test · mv_test_filtered</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -13244,9 +14950,15 @@
       <c r="D44" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
-      <c r="G44" s="12" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
@@ -13267,13 +14979,19 @@
       <c r="D45" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr"/>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_검색] S07 질의 입력 · [스모크20] 시트</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr"/>
-      <c r="G45" s="15" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr"/>
+      <c r="I45" s="15" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -13294,9 +15012,19 @@
       <c r="D46" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="11" t="inlineStr"/>
-      <c r="G46" s="12" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.read_table</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>smoke_q</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -13317,9 +15045,19 @@
       <c r="D47" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr"/>
-      <c r="G47" s="12" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_chunks · lab_search.Retriever · lab_search.api_search · set_index · ret.search · lab_search.llm_answer</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>HOW · corpus · ret</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -13340,9 +15078,19 @@
       <c r="D48" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="11" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>lab_eval.smoke_template · lab_io.save</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>smoke_tbl · smoke_path</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -13363,9 +15111,19 @@
       <c r="D49" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>smoke_path.replace · lab_io.read_table · lab_eval.smoke_summary</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>JUDGED · smoke_judged · smoke_result</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
@@ -13386,13 +15144,19 @@
       <c r="D50" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr"/>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_검색] S09~S12 · S15 평가</t>
         </is>
       </c>
-      <c r="F50" s="25" t="inlineStr"/>
-      <c r="G50" s="24" t="inlineStr"/>
+      <c r="H50" s="25" t="inlineStr"/>
+      <c r="I50" s="24" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -13413,9 +15177,19 @@
       <c r="D51" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr"/>
-      <c r="G51" s="12" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>golden.fillna · golden · lab_io.read_table · lab_io.sample_mod · golden.q_type.value_counts</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -13436,9 +15210,19 @@
       <c r="D52" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr"/>
-      <c r="G52" s="12" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_chunks · lab_search.Retriever · drop_duplicates · corpus.dropna · pd.concat</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>PARTS · BM25_TOK · CORPUS_N · corpus · ret</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -13459,9 +15243,19 @@
       <c r="D53" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>lab_eval.evaluate · ret.search</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>MODES · search_fn</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -13482,9 +15276,19 @@
       <c r="D54" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="11" t="inlineStr"/>
-      <c r="G54" s="12" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>lab_eval.breakdown</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>by_type · by_source</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -13505,9 +15309,19 @@
       <c r="D55" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="11" t="inlineStr"/>
-      <c r="G55" s="12" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · lab_eval.evaluate · sweep_rows.append · ret.search</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>sweep_rows · sweep · fn</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr"/>
+      <c r="I55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -13528,9 +15342,19 @@
       <c r="D56" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="11" t="inlineStr"/>
-      <c r="G56" s="12" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>failures.merge</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>MODE · failures</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -13551,9 +15375,19 @@
       <c r="D57" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="11" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>pd.concat · golden.set_index · ret.search</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>QID · drill</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr"/>
+      <c r="I57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -13574,9 +15408,19 @@
       <c r="D58" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="11" t="inlineStr"/>
-      <c r="G58" s="12" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>assign · lab_io.save · summary.reset_index</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>summary_out</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="15" t="inlineStr">
@@ -13597,13 +15441,19 @@
       <c r="D59" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr"/>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P3_정형연계] S22~S29 · [정형연계_패턴]</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr"/>
-      <c r="G59" s="15" t="inlineStr"/>
+      <c r="H59" s="14" t="inlineStr"/>
+      <c r="I59" s="15" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -13624,9 +15474,19 @@
       <c r="D60" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="11" t="inlineStr"/>
-      <c r="G60" s="12" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>lab_sql.load_catalog · lab_sql.allow_map</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -13647,9 +15507,19 @@
       <c r="D61" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="11" t="inlineStr"/>
-      <c r="G61" s="12" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>lab_sql.schema_prompt</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>schema_txt</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr"/>
+      <c r="I61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -13670,9 +15540,19 @@
       <c r="D62" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr"/>
-      <c r="G62" s="12" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · lab_sql.route · rows.append · map</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>QUESTIONS · rows · routing</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr"/>
+      <c r="I62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -13693,9 +15573,19 @@
       <c r="D63" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="11" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>lab_sql.make_sql · lab_sql.validate · lab_sql.explain</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>QUESTION · check</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr"/>
+      <c r="I63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -13716,9 +15606,19 @@
       <c r="D64" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="11" t="inlineStr"/>
-      <c r="G64" s="12" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · BAD.items · lab_sql.validate</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>BAD · guard</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -13739,9 +15639,19 @@
       <c r="D65" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr"/>
-      <c r="G65" s="12" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>lab_sql.answer_from_sql · lab_sql.run_sql · pd.DataFrame · pd.Timestamp.now</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>result · label · context</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="12" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -13762,9 +15672,19 @@
       <c r="D66" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="11" t="inlineStr"/>
-      <c r="G66" s="12" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>lab_sql.make_sql · lab_sql.validate · lab_io.load_chunks · lab_search.Retriever · _ret.search · lab_sql.run_sql</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>HYBRID_Q · chk_h · tbl_h · rag_h · mixed_context</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -13785,9 +15705,19 @@
       <c r="D67" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="11" t="inlineStr"/>
-      <c r="G67" s="12" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>golden_sql.itertuples · pd.DataFrame · pd.Series · lab_sample_sql.golden · lab_io.read_table · lab_sql.route</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>golden_sql · rows · sql_eval · summary_sql · rec · v</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr"/>
+      <c r="I67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -13808,9 +15738,15 @@
       <c r="D68" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="11" t="inlineStr"/>
-      <c r="G68" s="12" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · rename · summary_sql.rename</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
@@ -13831,13 +15767,19 @@
       <c r="D69" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E69" s="15" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr"/>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
         <is>
           <t>체크리스트: docs/rag_checklist_rev10.xlsx → [P1_검색] S15 평가</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr"/>
-      <c r="G69" s="15" t="inlineStr"/>
+      <c r="H69" s="14" t="inlineStr"/>
+      <c r="I69" s="15" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -13858,9 +15800,19 @@
       <c r="D70" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="11" t="inlineStr"/>
-      <c r="G70" s="12" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_raw · lab_search.Retriever · ret.search · dropna · lab_io.load_chunks</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>docs · chunks · ret · search_fn</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr"/>
+      <c r="I70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -13881,9 +15833,19 @@
       <c r="D71" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="11" t="inlineStr"/>
-      <c r="G71" s="12" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>lab_autoeval.make_known_item · lab_autoeval.sample_size_note</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>N_KNOWN · eval_known</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="12" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -13904,9 +15866,19 @@
       <c r="D72" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="11" t="inlineStr"/>
-      <c r="G72" s="12" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>lab_autoeval.make_title_query · lab_autoeval.make_dup_pair · eval_dup.head</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>eval_title · eval_dup</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -13927,9 +15899,19 @@
       <c r="D73" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="11" t="inlineStr"/>
-      <c r="G73" s="12" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>lab_autoeval.make_synthetic</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>N_SYN · eval_syn</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -13950,9 +15932,19 @@
       <c r="D74" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="11" t="inlineStr"/>
-      <c r="G74" s="12" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>pd.concat · eval_df.itertuples · pd.DataFrame · run · parts.append · search_fn</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>parts · detail · by_set · by_level · rows · res</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -13973,9 +15965,19 @@
       <c r="D75" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="11" t="inlineStr"/>
-      <c r="G75" s="12" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · crit.apply · got.get · crit.itertuples · pd.isna · replace</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>crit · got · thr · v</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -13996,9 +15998,19 @@
       <c r="D76" s="10" t="n">
         <v>103</v>
       </c>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="11" t="inlineStr"/>
-      <c r="G76" s="12" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>fails.head</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>fails</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -14019,9 +16031,15 @@
       <c r="D77" s="10" t="n">
         <v>108</v>
       </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="11" t="inlineStr"/>
-      <c r="G77" s="12" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>by_set.reset_index · lab_io.save</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
@@ -14042,13 +16060,19 @@
       <c r="D78" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
         <is>
           <t>기입 엑셀: archive/golden_eval_pack_rev4.xlsx → [1] [2] [3] 시트</t>
         </is>
       </c>
-      <c r="F78" s="14" t="inlineStr"/>
-      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="14" t="inlineStr"/>
+      <c r="I78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -14069,9 +16093,19 @@
       <c r="D79" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E79" s="5" t="inlineStr"/>
-      <c r="F79" s="11" t="inlineStr"/>
-      <c r="G79" s="12" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_raw · lab_autoeval.make_known_item · lab_autoeval.make_title_query · lab_autoeval.make_synthetic · dropna · sets.items</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>docs · chunks · sets</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr"/>
+      <c r="I79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -14092,9 +16126,19 @@
       <c r="D80" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="11" t="inlineStr"/>
-      <c r="G80" s="12" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>lab_autoeval.to_review · lab_io.save · review.head</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>review · review_path</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -14115,9 +16159,19 @@
       <c r="D81" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="11" t="inlineStr"/>
-      <c r="G81" s="12" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>review_path.replace · lab_io.read_table · lab_autoeval.from_review · golden.to_csv</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>REVIEWED · reviewed · golden</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="11" t="inlineStr"/>
+      <c r="I81" s="12" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -14138,9 +16192,19 @@
       <c r="D82" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="11" t="inlineStr"/>
-      <c r="G82" s="12" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>golden.fillna · lab_search.Retriever · lab_eval.evaluate · lab_io.read_table · ret.search · golden</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>golden · ret · search_fn</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -14161,9 +16225,19 @@
       <c r="D83" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="11" t="inlineStr"/>
-      <c r="G83" s="12" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>lab_autoeval.run_record · lab_io.save</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr"/>
+      <c r="I83" s="12" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -14184,9 +16258,19 @@
       <c r="D84" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="11" t="inlineStr"/>
-      <c r="G84" s="12" t="inlineStr"/>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · per_q.head</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>per_q</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
@@ -14207,13 +16291,19 @@
       <c r="D85" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E85" s="24" t="inlineStr">
+      <c r="E85" s="24" t="inlineStr"/>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
         <is>
           <t>기입 엑셀: archive/golden_eval_pack_rev4.xlsx → [7_답변평가] [8_표준지표]</t>
         </is>
       </c>
-      <c r="F85" s="25" t="inlineStr"/>
-      <c r="G85" s="24" t="inlineStr"/>
+      <c r="H85" s="25" t="inlineStr"/>
+      <c r="I85" s="24" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -14234,9 +16324,19 @@
       <c r="D86" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="11" t="inlineStr"/>
-      <c r="G86" s="12" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>os.path.basename · lab_io.read_table · gold.q_type.value_counts · gold.head</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>SRC · gold</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -14257,9 +16357,19 @@
       <c r="D87" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="11" t="inlineStr"/>
-      <c r="G87" s="12" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>lab_ragas.catalog</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr"/>
+      <c r="I87" s="12" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -14280,9 +16390,19 @@
       <c r="D88" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="11" t="inlineStr"/>
-      <c r="G88" s="12" t="inlineStr"/>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.Retriever · set_index · itertuples · ret.search · tolist · lab_search.llm_answer</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>corpus · ret · meta · rows · res · ctx</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr"/>
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -14303,9 +16423,19 @@
       <c r="D89" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="11" t="inlineStr"/>
-      <c r="G89" s="12" t="inlineStr"/>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.Embedder · lab_ragas.evaluate_answers</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>emb · auto · num</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="11" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -14326,9 +16456,19 @@
       <c r="D90" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="11" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame · lab_ragas.judge_prompt · jr.append · lab_ragas.parse_judge · lab_search.llm_answer · judge.mean</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>jr · judge · p</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -14349,9 +16489,19 @@
       <c r="D91" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="11" t="inlineStr"/>
-      <c r="G91" s="12" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>THRESH.get · T.rename · pd.isna · pd.DataFrame · auto.faithfulness.mean · auto.answer_relevancy.mean</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>summary · THRESH</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr"/>
+      <c r="I91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -14372,9 +16522,15 @@
       <c r="D92" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="11" t="inlineStr"/>
-      <c r="G92" s="12" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · rename · summary.reset_index</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr"/>
+      <c r="I92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
@@ -14395,13 +16551,19 @@
       <c r="D93" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E93" s="15" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr"/>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>기입 엑셀: archive/golden_eval_pack_rev4.xlsx → [2d_근거문서_연결] [2e_원본_수집목록]</t>
         </is>
       </c>
-      <c r="F93" s="14" t="inlineStr"/>
-      <c r="G93" s="15" t="inlineStr"/>
+      <c r="H93" s="14" t="inlineStr"/>
+      <c r="I93" s="15" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -14422,9 +16584,19 @@
       <c r="D94" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="11" t="inlineStr"/>
-      <c r="G94" s="12" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.read_table · bank.head</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr"/>
+      <c r="I94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -14445,9 +16617,19 @@
       <c r="D95" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="11" t="inlineStr"/>
-      <c r="G95" s="12" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>set_index · lab_search.Retriever · lab_autoeval.link_evidence · lab_io.save · ret.search · bank.head</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>K · corpus · meta · ret · search_fn · linked</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr"/>
+      <c r="I95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -14468,9 +16650,19 @@
       <c r="D96" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="11" t="inlineStr"/>
-      <c r="G96" s="12" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>link_path.replace · lab_io.read_table · lab_autoeval.apply_evidence · lab_autoeval.coverage_report · golden.to_csv · pd.DataFrame</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>LINKED · done · rep</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="11" t="inlineStr"/>
+      <c r="I96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -14491,9 +16683,19 @@
       <c r="D97" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="11" t="inlineStr"/>
-      <c r="G97" s="12" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>merge · lab_io.save · gap.head</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="11" t="inlineStr"/>
+      <c r="I97" s="12" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -14514,9 +16716,15 @@
       <c r="D98" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="E98" s="5" t="inlineStr"/>
-      <c r="F98" s="11" t="inlineStr"/>
-      <c r="G98" s="12" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>lab_eval.evaluate · lab_io.save · golden.fillna · ret.search</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="11" t="inlineStr"/>
+      <c r="I98" s="12" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="24" t="inlineStr">
@@ -14537,13 +16745,19 @@
       <c r="D99" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="E99" s="24" t="inlineStr"/>
+      <c r="F99" s="24" t="inlineStr">
+        <is>
+          <t>USE_LLM · LAB</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
         <is>
           <t>기입 엑셀: archive/golden_eval_pack_rev4.xlsx → [1b_LLM골든셋_검수]</t>
         </is>
       </c>
-      <c r="F99" s="25" t="inlineStr"/>
-      <c r="G99" s="24" t="inlineStr"/>
+      <c r="H99" s="25" t="inlineStr"/>
+      <c r="I99" s="24" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -14564,9 +16778,19 @@
       <c r="D100" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="E100" s="5" t="inlineStr"/>
-      <c r="F100" s="11" t="inlineStr"/>
-      <c r="G100" s="12" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.load_raw · dropna · lab_golden_llm.sample_chunks · lab_io.load_chunks · size · sampled.groupby</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>raw · chunks · sampled</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="11" t="inlineStr"/>
+      <c r="I100" s="12" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -14587,9 +16811,19 @@
       <c r="D101" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="E101" s="5" t="inlineStr"/>
-      <c r="F101" s="11" t="inlineStr"/>
-      <c r="G101" s="12" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>lab_golden_llm.generate · gen.head</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>N · gen</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="11" t="inlineStr"/>
+      <c r="I101" s="12" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -14610,9 +16844,19 @@
       <c r="D102" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="11" t="inlineStr"/>
-      <c r="G102" s="12" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.Retriever · lab_golden_llm.self_check · lab_golden_llm.apply_check · chunks.reset_index · size · chk.groupby</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>ret · chk · gen</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="11" t="inlineStr"/>
+      <c r="I102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -14633,9 +16877,19 @@
       <c r="D103" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="E103" s="5" t="inlineStr"/>
-      <c r="F103" s="11" t="inlineStr"/>
-      <c r="G103" s="12" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>lab_golden_llm.make_unanswerable · pd.concat</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>noans · gold</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="11" t="inlineStr"/>
+      <c r="I103" s="12" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -14656,9 +16910,19 @@
       <c r="D104" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="11" t="inlineStr"/>
-      <c r="G104" s="12" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>lab_golden_llm.mix_report</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="11" t="inlineStr"/>
+      <c r="I104" s="12" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -14679,9 +16943,19 @@
       <c r="D105" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="11" t="inlineStr"/>
-      <c r="G105" s="12" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>lab_golden_llm.to_review · lab_io.save</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="11" t="inlineStr"/>
+      <c r="I105" s="12" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -14702,9 +16976,19 @@
       <c r="D106" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="E106" s="5" t="inlineStr"/>
-      <c r="F106" s="11" t="inlineStr"/>
-      <c r="G106" s="12" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>lab_golden_llm.finalize · final.to_csv · pd.DataFrame · lab_io.read_table · size · final.groupby</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>REVIEWED · final</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="11" t="inlineStr"/>
+      <c r="I106" s="12" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -14726,8 +17010,10 @@
         <v>77</v>
       </c>
       <c r="E107" s="5" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr"/>
-      <c r="G107" s="12" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="11" t="inlineStr"/>
+      <c r="I107" s="12" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="24" t="inlineStr">
@@ -14748,13 +17034,19 @@
       <c r="D108" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E108" s="24" t="inlineStr">
+      <c r="E108" s="24" t="inlineStr"/>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>LAB · LG</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
         <is>
           <t>기입 엑셀: archive/rag_project_log_rev1.xlsx → [5_실험이력] [6_프리셋비교]</t>
         </is>
       </c>
-      <c r="F108" s="25" t="inlineStr"/>
-      <c r="G108" s="24" t="inlineStr"/>
+      <c r="H108" s="25" t="inlineStr"/>
+      <c r="I108" s="24" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -14775,9 +17067,15 @@
       <c r="D109" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="11" t="inlineStr"/>
-      <c r="G109" s="12" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>pd.DataFrame</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="11" t="inlineStr"/>
+      <c r="I109" s="12" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -14798,9 +17096,19 @@
       <c r="D110" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="E110" s="5" t="inlineStr"/>
-      <c r="F110" s="11" t="inlineStr"/>
-      <c r="G110" s="12" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>set_index · lab_search.Retriever · lab_graph.cfg · lab_graph.build_langgraph · dropna · lab_io.load_raw</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>corpus · meta · ret · conf · app</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="11" t="inlineStr"/>
+      <c r="I110" s="12" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -14821,9 +17129,19 @@
       <c r="D111" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="11" t="inlineStr"/>
-      <c r="G111" s="12" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>lab_graph.run_graph · lab_graph.trace_table</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Q · st · tr</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="11" t="inlineStr"/>
+      <c r="I111" s="12" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -14844,9 +17162,19 @@
       <c r="D112" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="E112" s="5" t="inlineStr"/>
-      <c r="F112" s="11" t="inlineStr"/>
-      <c r="G112" s="12" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>os.path.basename · lab_io.read_table · gold.qid.astype · gold.question.astype</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>GSRC · gold · qs</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="11" t="inlineStr"/>
+      <c r="I112" s="12" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -14867,9 +17195,19 @@
       <c r="D113" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="11" t="inlineStr"/>
-      <c r="G113" s="12" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>lab_search.Embedder · lab_graph.compare</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>emb · PRESETS</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="11" t="inlineStr"/>
+      <c r="I113" s="12" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -14890,9 +17228,19 @@
       <c r="D114" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="E114" s="5" t="inlineStr"/>
-      <c r="F114" s="11" t="inlineStr"/>
-      <c r="G114" s="12" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>lab_graph.delta</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="12" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -14913,9 +17261,19 @@
       <c r="D115" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="11" t="inlineStr"/>
-      <c r="G115" s="12" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>detail.pivot_table · piv.round</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>M · piv</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="12" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -14936,16 +17294,62 @@
       <c r="D116" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E116" s="5" t="inlineStr"/>
-      <c r="F116" s="11" t="inlineStr"/>
-      <c r="G116" s="12" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>lab_io.save · detail.drop</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="11" t="inlineStr"/>
+      <c r="I116" s="12" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>전체 셀</t>
+        </is>
+      </c>
+      <c r="B119" s="18">
+        <f>COUNTIF(C5:C116,"&lt;&gt;")</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>확인 완료</t>
+        </is>
+      </c>
+      <c r="B120" s="18">
+        <f>COUNTIF(H5:H116,"확인")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>진행률</t>
+        </is>
+      </c>
+      <c r="B121" s="19">
+        <f>IFERROR(COUNTIF(H5:H116,"확인")/COUNTIF(C5:C116,"&lt;&gt;"),"")</f>
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F116">
+  <conditionalFormatting sqref="H5:H116">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"확인"</formula>
     </cfRule>
@@ -14954,7 +17358,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확인,보류,질문 있음"</formula1>
     </dataValidation>
   </dataValidations>
